--- a/thermalHydraulicsTransitoire/resultsDFM.xlsx
+++ b/thermalHydraulicsTransitoire/resultsDFM.xlsx
@@ -453,7 +453,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.01295</v>
+        <v>0.01296</v>
       </c>
     </row>
     <row r="3">
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12">
@@ -554,7 +554,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>[0, 0, 0, 0, 0, 258343621.99656138, 464111294.07304585, 643121048.9477705, 801616884.5533046, 939181059.631159, 1051127090.8494016, 1126310112.752174, 1122408289.3445165, 1081172180.4437337, 1031843496.2872249, 983894892.2989957, 937681015.0227087, 895327431.5813872, 856202572.3278213, 819006748.3864719, 783458145.5906223, 750100828.0210507, 718554804.5340585, 688552978.61663, 659925941.6264193, 632555952.3337886, 606361552.3049375, 581310949.6292913, 557313881.9593534, 534243804.1517887, 511696758.85338926, 490163408.6280137, 469534771.69549954, 449740016.56838495, 430717871.56447715, 412422182.83317775, 394814088.65443784, 377859707.29978603, 361528202.8391785, 345790873.6246813, 330620929.96940905, 315992916.1128045, 301882465.66746414, 288266501.7080876, 275122569.80833167, 262429438.3076382, 250166275.72334605, 238313317.7138493, 226851289.04385388, 215761603.6733368, 205026564.8464833, 194629231.69905567, 184555197.82682595, 174786210.67134607, 165307052.35654178, 156123870.05952707, 147165287.60625303, 138440542.436471, 129936873.3217376, 121641063.27545929, 113539795.26656306, 105619818.9602932, 97868395.36031584, 90271840.60582201, 82817826.99442658, 75493593.29768783, 68286244.8945373, 61182464.753902555, 54167929.84194744, 47226216.19088542, 40337009.21450338, 33472607.709604003, 26591637.728233684, 19627619.71753486, 12467706.29004373]</t>
+          <t>[258343621.99656138, 464111294.07304585, 643121048.9477705, 801616884.5533046, 939181059.631159, 1051127090.8494016, 1126310112.752174, 1122408289.3445165, 1081172180.4437337, 1031843496.2872249, 983894892.2989957, 937681015.0227087, 895327431.5813872, 856202572.3278213, 819006748.3864719, 783458145.5906223, 750100828.0210507, 718554804.5340585, 688552978.61663, 659925941.6264193, 632555952.3337886, 606361552.3049375, 581310949.6292913, 557313881.9593534, 534243804.1517887, 511696758.85338926, 490163408.6280137, 469534771.69549954, 449740016.56838495, 430717871.56447715, 412422182.83317775, 394814088.65443784, 377859707.29978603, 361528202.8391785, 345790873.6246813, 330620929.96940905, 315992916.1128045, 301882465.66746414, 288266501.7080876, 275122569.80833167, 262429438.3076382, 250166275.72334605, 238313317.7138493, 226851289.04385388, 215761603.6733368, 205026564.8464833, 194629231.69905567, 184555197.82682595, 174786210.67134607, 165307052.35654178, 156123870.05952707, 147165287.60625303, 138440542.436471, 129936873.3217376, 121641063.27545929, 113539795.26656306, 105619818.9602932, 97868395.36031584, 90271840.60582201, 82817826.99442658, 75493593.29768783, 68286244.8945373, 61182464.753902555, 54167929.84194744, 47226216.19088542, 40337009.21450338, 33472607.709604003, 26591637.728233684, 19627619.71753486, 12467706.29004373]</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.75617301898581e-06</v>
+        <v>1.887369670341939e-06</v>
       </c>
     </row>
     <row r="14">
@@ -612,7 +612,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>FVM</t>
+          <t>BiCG</t>
         </is>
       </c>
     </row>
@@ -627,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -647,598 +647,558 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>543.1499999999999</v>
+        <v>543.1500000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
-        <v>543.1496151605397</v>
+        <v>544.7096035615455</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
-        <v>543.149230327101</v>
+        <v>546.857754007734</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
-        <v>543.1488455005608</v>
+        <v>549.5135412558592</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
-        <v>543.1484606802685</v>
+        <v>552.5931872351431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
-        <v>543.9592214613782</v>
+        <v>555.9972464723224</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
-        <v>545.4107633799217</v>
+        <v>559.5921694457293</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>547.4108770387724</v>
+        <v>561.7345679893092</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>549.8848845453908</v>
+        <v>561.7267041088353</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>552.7555669331424</v>
+        <v>561.7186475376818</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>555.9311867306026</v>
+        <v>561.710127223676</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>559.2881535362585</v>
+        <v>561.7011660727798</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>561.5819328222346</v>
+        <v>561.6917977434907</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>561.5774992736965</v>
+        <v>561.6820538670479</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>561.5729782141148</v>
+        <v>561.6719622237005</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>561.5681464908525</v>
+        <v>561.6615482971391</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>561.5629921512722</v>
+        <v>561.6508335115251</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>561.5575092384006</v>
+        <v>561.6398371238963</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>561.5516964225452</v>
+        <v>561.6285765071644</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>561.5455538666524</v>
+        <v>561.6170674002014</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>561.5390851102449</v>
+        <v>561.6053241250893</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>561.5322942954691</v>
+        <v>561.5933597629876</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>561.5251867512474</v>
+        <v>561.5811921579705</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>561.5177687377704</v>
+        <v>561.5688249022079</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>561.5100471341966</v>
+        <v>561.5562711166534</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>561.5020292323325</v>
+        <v>561.5435410412844</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>561.4937225782977</v>
+        <v>561.5306436295265</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>561.485134820262</v>
+        <v>561.5175873222357</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>561.4762736891297</v>
+        <v>561.5043800310731</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>561.4671538132922</v>
+        <v>561.4910291922079</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>561.4577751763013</v>
+        <v>561.4775418049247</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>561.4481484440452</v>
+        <v>561.4639244687797</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>561.4382814990666</v>
+        <v>561.4501834167183</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>561.4281821212176</v>
+        <v>561.436324545142</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>561.4178579785283</v>
+        <v>561.4223534410382</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>561.4073166128657</v>
+        <v>561.4082754061368</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>561.3965654312276</v>
+        <v>561.3940954788904</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>561.3856116994319</v>
+        <v>561.3798184544501</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>561.3744625382471</v>
+        <v>561.3654489024703</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>561.3631249212752</v>
+        <v>561.3509911838089</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>561.3516056738807</v>
+        <v>561.3364494652045</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>561.3399114734091</v>
+        <v>561.3218277333589</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>561.3280488503084</v>
+        <v>561.3071298073014</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>561.3160241896592</v>
+        <v>561.2923593501873</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>561.3038437337527</v>
+        <v>561.277519880047</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>561.2915135845697</v>
+        <v>561.2626147795046</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>561.2790397072738</v>
+        <v>561.2476473048018</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>561.2664279334573</v>
+        <v>561.2326205923109</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>561.2536839650388</v>
+        <v>561.2175376702634</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>561.2408133782365</v>
+        <v>561.2024014644078</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>561.2278216274274</v>
+        <v>561.1872147839327</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>561.2147140491121</v>
+        <v>561.1720063772777</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>561.2014958638827</v>
+        <v>561.1567365379722</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>561.188172184327</v>
+        <v>561.1414246366742</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>561.1747721036436</v>
+        <v>561.1260731948222</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>561.1612666404305</v>
+        <v>561.1106846710072</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>561.1476711357602</v>
+        <v>561.0952614665371</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>561.1339903177072</v>
+        <v>561.0798059303734</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>561.1202288301536</v>
+        <v>561.0643203653592</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>561.1063912387197</v>
+        <v>561.0488070318911</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>561.0924820362414</v>
+        <v>561.033268153664</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>561.0785056479307</v>
+        <v>561.0177059224511</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>561.0644664363622</v>
+        <v>561.002122503469</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>561.0503687079139</v>
+        <v>560.9865200413335</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>561.0362167173786</v>
+        <v>560.9709006673646</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>561.0220146739056</v>
+        <v>560.9552665093087</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>561.0077667469841</v>
+        <v>560.9396197056967</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>560.9934770729534</v>
+        <v>560.9239624287732</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>560.9791497625447</v>
+        <v>560.9082969230591</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>560.9647889103134</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>560.950398607452</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>560.9359829608962</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>560.9215461239669</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>560.90709234806</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
         <v>560.892626073233</v>
       </c>
     </row>
@@ -1253,7 +1213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1278,7 +1238,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
         <v>0.0001</v>
@@ -1286,7 +1246,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
         <v>0.0001</v>
@@ -1294,7 +1254,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
         <v>0.0001</v>
@@ -1302,7 +1262,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
         <v>0.0001</v>
@@ -1310,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
         <v>0.0001</v>
@@ -1318,7 +1278,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
         <v>0.0001</v>
@@ -1326,546 +1286,506 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0001</v>
+        <v>0.08219214403438109</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>0.0001</v>
+        <v>0.1939146266027441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0001</v>
+        <v>0.2766100124395202</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0001</v>
+        <v>0.3394786545150288</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0001</v>
+        <v>0.3884301808897367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>0.06619084907136882</v>
+        <v>0.4276175769626816</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>0.1762355904243766</v>
+        <v>0.4597318414421821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2575838582431387</v>
+        <v>0.4865686210242853</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>0.3202136726189887</v>
+        <v>0.509339842199522</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>0.3693699195552578</v>
+        <v>0.5289344300670961</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4089312542802177</v>
+        <v>0.5459922861669498</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>0.4414538045565928</v>
+        <v>0.5609876855070788</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>0.4687019268228289</v>
+        <v>0.5742807016089658</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>0.4918677374503431</v>
+        <v>0.5861502109893558</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>0.5118281039281469</v>
+        <v>0.5968160115375347</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5292214569828055</v>
+        <v>0.6063733163836271</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>0.5445224632494841</v>
+        <v>0.6150987605474094</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>0.5580927780967997</v>
+        <v>0.6230499012942007</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>0.5702133558706847</v>
+        <v>0.6303162098262295</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>0.5811062208045948</v>
+        <v>0.6369818796657749</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>0.5909499006717553</v>
+        <v>0.6431160035219454</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>0.5998887635894112</v>
+        <v>0.6487768687917285</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>0.6079542934754852</v>
+        <v>0.6540140350796206</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>0.6153860527672803</v>
+        <v>0.6588700267798249</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>0.6222039155686893</v>
+        <v>0.6633815910325249</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>0.6284782700443127</v>
+        <v>0.667580681642666</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>0.6342685365081406</v>
+        <v>0.6714952349177031</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>0.639625268391262</v>
+        <v>0.6751497929938454</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>0.6445918672527081</v>
+        <v>0.6785660135837525</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>0.6492058578695699</v>
+        <v>0.6817630859438668</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>0.653499886269586</v>
+        <v>0.684758074663162</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>0.6575025071363675</v>
+        <v>0.6875662092736879</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>0.6612388167883597</v>
+        <v>0.6902011219575601</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>0.6647309711226483</v>
+        <v>0.6926750539644964</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>0.667998608442459</v>
+        <v>0.6949990239150668</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>0.6710591990671887</v>
+        <v>0.6971829772329795</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>0.6739283399922786</v>
+        <v>0.6992359094618704</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>0.6766199967935191</v>
+        <v>0.7011659740968088</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>0.679146713812006</v>
+        <v>0.7029805775359576</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>0.6815197855493769</v>
+        <v>0.7046864605143004</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>0.6837494089440461</v>
+        <v>0.7062897838659034</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>0.6858448090501666</v>
+        <v>0.7077961522225078</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>0.6878143489917345</v>
+        <v>0.7092106883963696</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>0.6896656268317048</v>
+        <v>0.7105382476431569</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>0.6914055586759271</v>
+        <v>0.7115764562444271</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>0.6930404662929545</v>
+        <v>0.7127336194341609</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>0.6945761011703442</v>
+        <v>0.7138154083172301</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>0.695836168173542</v>
+        <v>0.714825058350396</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>0.6971806558093618</v>
+        <v>0.7157655240532202</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>0.6984404327211277</v>
+        <v>0.71663949847324</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>0.6996194532593804</v>
+        <v>0.7174494338030454</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>0.7007213411767058</v>
+        <v>0.7181975488975465</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>0.7017494106825601</v>
+        <v>0.7188858526120002</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7027066875950525</v>
+        <v>0.719516151857268</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>0.7035959292790556</v>
+        <v>0.7200900606292335</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>0.7044196457681385</v>
+        <v>0.7206090056562718</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>0.7051801074590485</v>
+        <v>0.7210742266432112</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>0.7058793690190507</v>
+        <v>0.7214867674883645</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>0.7065192776398709</v>
+        <v>0.7218474535142101</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>0.7071014822793594</v>
+        <v>0.7221568422989127</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>0.7076274394342217</v>
+        <v>0.7224151277628327</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>0.7080984133776087</v>
+        <v>0.7226219598242075</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>0.7085154671317473</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>0.708879439101932</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>0.70919089263573</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>0.7094500176404335</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>0.7096564456147996</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
-        <v>0.7098089040208869</v>
+        <v>0.7227724056458896</v>
       </c>
     </row>
   </sheetData>
@@ -1879,7 +1799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,599 +1819,559 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>734.5634695481847</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
-        <v>734.5841170733678</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
-        <v>734.6047654922955</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
-        <v>734.625414805577</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
-        <v>734.6460650138156</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
-        <v>734.6667161176242</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
-        <v>734.6873681176136</v>
+        <v>734.5102355052903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>734.7080210143951</v>
+        <v>677.3519546101707</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>734.7286748085708</v>
+        <v>599.5635075313222</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>734.7493295007544</v>
+        <v>541.9854193457309</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>734.7699850915581</v>
+        <v>498.212267180954</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>734.7906415815927</v>
+        <v>464.1293408477512</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>688.7565468228722</v>
+        <v>436.8449582278297</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>612.0896168513896</v>
+        <v>414.4853981614017</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>555.4151561691862</v>
+        <v>395.8003663139875</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>511.7818366778724</v>
+        <v>379.946015200263</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>477.5355983552113</v>
+        <v>366.3033951540131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>449.9741720493627</v>
+        <v>354.4269523840791</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>427.3166896039068</v>
+        <v>343.9864588627617</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>408.3339076650206</v>
+        <v>334.7312047030291</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>392.1952689563626</v>
+        <v>326.4670170026909</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>378.2898492274137</v>
+        <v>319.0408587383611</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>366.17284564883</v>
+        <v>312.3864747451733</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>355.5135520906187</v>
+        <v>306.3111972528562</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>346.059998954323</v>
+        <v>300.7749800323012</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>337.6164422465977</v>
+        <v>295.7155347729749</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>330.0281954950985</v>
+        <v>291.074242649094</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>323.1708767932208</v>
+        <v>286.8030001537973</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>316.9439039929329</v>
+        <v>282.8612273890966</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>311.3253685220794</v>
+        <v>279.2144214771476</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>306.1483256996088</v>
+        <v>275.8329779527623</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>301.3989485422571</v>
+        <v>272.6913148357101</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>297.0281983574438</v>
+        <v>269.7671875268996</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>292.9946781265971</v>
+        <v>267.04114860189</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>289.2631686961871</v>
+        <v>264.4961138019155</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>285.8034338380711</v>
+        <v>262.1170071085341</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>282.5893318422648</v>
+        <v>259.8904711199153</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>279.5981201490059</v>
+        <v>257.8046276851932</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>276.8099067368871</v>
+        <v>255.8488762595868</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>274.2072091065864</v>
+        <v>254.0137284044045</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>271.7745934124365</v>
+        <v>252.2906640671789</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>269.4983798663195</v>
+        <v>250.6720144072179</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>267.3663991550704</v>
+        <v>249.1508577538162</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>265.367787141482</v>
+        <v>247.7209337532779</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>263.4928163254457</v>
+        <v>246.376568295717</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>261.7327494008981</v>
+        <v>245.1126074072664</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>260.079719843903</v>
+        <v>243.9243605553226</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>258.5266258170562</v>
+        <v>242.807540919786</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>257.0670426088607</v>
+        <v>241.7582489468786</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>255.6951460277648</v>
+        <v>240.772920538779</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>254.4056449113503</v>
+        <v>239.8481776313441</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>253.1937232269112</v>
+        <v>239.1252380290094</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>252.0549790111582</v>
+        <v>238.3192179958889</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>250.9854076471985</v>
+        <v>237.5657141570017</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>250.1080268873839</v>
+        <v>236.862476642708</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>249.1716673274122</v>
+        <v>236.2074512328071</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>248.2943431552929</v>
+        <v>235.5987658161055</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>247.4733019741274</v>
+        <v>235.0347160424558</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>246.7060217420693</v>
+        <v>234.5137601149501</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>245.9901961153067</v>
+        <v>234.034502537122</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>245.3237197211576</v>
+        <v>233.5956885243945</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>244.7046742757918</v>
+        <v>233.196197734171</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>244.1313138730909</v>
+        <v>232.8350403555224</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>243.6020596437459</v>
+        <v>232.5113569708715</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>243.1154830958467</v>
+        <v>232.2244247211893</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>242.6703003797685</v>
+        <v>231.9736732402667</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>242.2653658627084</v>
+        <v>231.7587190302676</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>241.8996681241572</v>
+        <v>231.5794324948483</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>241.5723298157401</v>
+        <v>231.4360639631462</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>241.2826139911651</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>241.0299404514137</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>240.813921002924</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>240.6344282084524</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>240.4917246320264</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
-        <v>240.3867043367068</v>
+        <v>231.3320647094314</v>
       </c>
     </row>
   </sheetData>
@@ -2505,7 +2385,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2525,598 +2405,558 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7286831.124624791</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
-        <v>7285661.154487603</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
-        <v>7284491.184533521</v>
+        <v>7289847.809569028</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
-        <v>7283321.214752246</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
-        <v>7282151.245133477</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
-        <v>7280981.275666908</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
-        <v>7279811.306342238</v>
+        <v>7289847.809569029</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>7278641.337149153</v>
+        <v>7289413.497140932</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>7277471.368077349</v>
+        <v>7288574.451003737</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>7276301.399116509</v>
+        <v>7287714.922111515</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>7275131.430256322</v>
+        <v>7286806.002382274</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>7273961.461486472</v>
+        <v>7285850.149140689</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>7273141.098363669</v>
+        <v>7284850.96620583</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>7272668.854410967</v>
+        <v>7283811.840333281</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>7272187.313280923</v>
+        <v>7282735.746723253</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>7271672.710108237</v>
+        <v>7281625.414847472</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>7271123.777355127</v>
+        <v>7280483.140551311</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>7270539.886616411</v>
+        <v>7279310.987932796</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>7269920.902748788</v>
+        <v>7278110.819575878</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>7269266.849962868</v>
+        <v>7276884.323264346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>7268578.112348552</v>
+        <v>7275633.035192766</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>7267855.138424814</v>
+        <v>7274358.358756947</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>7267098.503282654</v>
+        <v>7273062.204120952</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>7266308.881321366</v>
+        <v>7271744.962697127</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>7265487.012945402</v>
+        <v>7270408.040529628</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>7264633.682555854</v>
+        <v>7269052.536259292</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>7263749.70165419</v>
+        <v>7267679.411056964</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>7262835.892604872</v>
+        <v>7266289.571085077</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>7261893.086547621</v>
+        <v>7264883.865752771</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>7260922.848334023</v>
+        <v>7263463.093455984</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>7259925.184646176</v>
+        <v>7262028.005710399</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>7258901.238568871</v>
+        <v>7260579.311127103</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>7257851.856921581</v>
+        <v>7259117.678955617</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>7256777.875442471</v>
+        <v>7257643.742303552</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>7255680.117802658</v>
+        <v>7256158.101039129</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>7254559.3940664</v>
+        <v>7254661.324377136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>7253416.499754112</v>
+        <v>7253153.95323338</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>7252252.21516163</v>
+        <v>7251636.502362406</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>7251067.30493944</v>
+        <v>7250109.462265031</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>7249862.517860157</v>
+        <v>7248573.300976369</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>7248638.586700124</v>
+        <v>7247028.465638476</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>7247396.228255463</v>
+        <v>7245475.384008366</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>7246136.143459123</v>
+        <v>7243914.465782231</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>7244859.01753912</v>
+        <v>7242346.103860131</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>7243565.520290435</v>
+        <v>7240770.67549745</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>7242256.306336403</v>
+        <v>7239188.543345602</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>7240932.015499061</v>
+        <v>7237600.056419143</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>7239593.273142834</v>
+        <v>7236005.550795957</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>7238240.690588955</v>
+        <v>7234405.350869875</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>7236874.865537244</v>
+        <v>7232799.769958385</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>7235496.382476998</v>
+        <v>7231189.108816828</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>7234105.813108196</v>
+        <v>7229576.418354171</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>7232703.716552291</v>
+        <v>7227957.490344351</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>7231290.640193116</v>
+        <v>7226334.381273456</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>7229869.67388137</v>
+        <v>7224707.360615815</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>7228437.748707958</v>
+        <v>7223076.69100855</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>7226996.495902512</v>
+        <v>7221442.628843992</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>7225546.420913535</v>
+        <v>7219805.424798511</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>7224088.019986612</v>
+        <v>7218165.324495079</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>7222621.78079416</v>
+        <v>7216522.568895895</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>7221148.183018748</v>
+        <v>7214877.394913369</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>7219667.698901139</v>
+        <v>7213230.035919245</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>7218180.793771338</v>
+        <v>7211580.722314216</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>7216687.926730826</v>
+        <v>7209929.682160286</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>7215189.551144526</v>
+        <v>7208277.14195569</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>7213686.115269413</v>
+        <v>7206623.327662614</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>7212178.062889973</v>
+        <v>7204968.466227044</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>7210665.834008604</v>
+        <v>7203312.788000721</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>7209149.865642759</v>
+        <v>7201656.530815565</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>7207630.592824885</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>7206108.449955771</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>7204583.872824761</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>7203057.301846791</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>7201529.18752177</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
         <v>7200000</v>
       </c>
     </row>
@@ -3131,7 +2971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,599 +2991,559 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.288875789436323</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
-        <v>1.288839561966058</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
-        <v>1.288803334966562</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
-        <v>1.288767108432004</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
-        <v>1.288730882364979</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
-        <v>1.288694656766537</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
-        <v>1.288658431630759</v>
+        <v>1.284938054532655</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>1.288622206961246</v>
+        <v>1.393367334076205</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>1.28858598275221</v>
+        <v>1.574145345541969</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>1.288549759007677</v>
+        <v>1.741375467249789</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>1.288513535721072</v>
+        <v>1.894373497777921</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>1.288477312895626</v>
+        <v>2.033485133594175</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>1.374595459914599</v>
+        <v>2.160492172380397</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>1.546769466398774</v>
+        <v>2.277040674628187</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>1.70460148117897</v>
+        <v>2.384535711934177</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>1.849931727624756</v>
+        <v>2.484037384773969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>1.982598619028065</v>
+        <v>2.576552978297104</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>2.104034944726894</v>
+        <v>2.662890322864655</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>2.215596476213499</v>
+        <v>2.74371294392952</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>2.318595903268484</v>
+        <v>2.819576079489841</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>2.414004902705625</v>
+        <v>2.890950837010171</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>2.502740382028906</v>
+        <v>2.958242082513335</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>2.585558364217809</v>
+        <v>3.021257861524588</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>2.663080611763463</v>
+        <v>3.081180510410703</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>2.735829729603257</v>
+        <v>3.137894281095782</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>2.80425092437046</v>
+        <v>3.191581020710814</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>2.868728251566413</v>
+        <v>3.242472017888777</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>2.929599370154626</v>
+        <v>3.290760853459981</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>2.987156953653463</v>
+        <v>3.336618782801349</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>3.041066589316391</v>
+        <v>3.38019819294662</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>3.092491736565653</v>
+        <v>3.421636124280866</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>3.141222499914268</v>
+        <v>3.461056619725693</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>3.187445351809032</v>
+        <v>3.498572557093568</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>3.231325388519793</v>
+        <v>3.534287066862908</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>3.273009621589827</v>
+        <v>3.568294683041539</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>3.312630341776523</v>
+        <v>3.600682327775165</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>3.350307363444662</v>
+        <v>3.631530121037993</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>3.386149776441674</v>
+        <v>3.660912068373563</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>3.420257302385882</v>
+        <v>3.68889668502147</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>3.452721396077244</v>
+        <v>3.71554748692039</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>3.483626188056326</v>
+        <v>3.740923479711058</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>3.513049259900666</v>
+        <v>3.765079519723107</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>3.541062302651203</v>
+        <v>3.788066695005507</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>3.56773171443251</v>
+        <v>3.809932615101793</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>3.593119070599433</v>
+        <v>3.83072168803209</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>3.617281592005333</v>
+        <v>3.850475388438456</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>3.640272490726213</v>
+        <v>3.869232489420702</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>3.662141335084311</v>
+        <v>3.887029438333719</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>3.682934327395009</v>
+        <v>3.903900123682243</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>3.702694569580275</v>
+        <v>3.919876265111859</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>3.721462320302102</v>
+        <v>3.934989476819541</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>3.73927521751576</v>
+        <v>3.946885999551816</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>3.756168638377171</v>
+        <v>3.960234766795027</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>3.772175477957419</v>
+        <v>3.972795715134623</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>3.78540827987101</v>
+        <v>3.984590819043863</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>3.799633391129098</v>
+        <v>3.995640456717266</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>3.813059000920463</v>
+        <v>4.005963458881946</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>3.825709541832637</v>
+        <v>4.015577192922322</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>3.837607848195128</v>
+        <v>4.024497509926134</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>3.848775165297134</v>
+        <v>4.032738898677382</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>3.859231187184786</v>
+        <v>4.040314469563373</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>3.86899410565021</v>
+        <v>4.047235966416289</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>3.878080691801002</v>
+        <v>4.053513747577719</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>3.88650624742274</v>
+        <v>4.059156712001917</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>3.894284751530483</v>
+        <v>4.064172124150541</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>3.901428848472787</v>
+        <v>4.068565275172407</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>3.907949858932544</v>
+        <v>4.072338826413038</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>3.913857763261862</v>
+        <v>4.075491583306518</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>3.91916113197682</v>
+        <v>4.0780162345317</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>3.923866959815893</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>3.927980343740596</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>3.931503858299475</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>3.934436388414058</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>3.936770976505025</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
-        <v>3.938490837440998</v>
+        <v>4.079849568091001</v>
       </c>
     </row>
   </sheetData>
@@ -3757,7 +3557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B76"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3777,599 +3577,559 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1184505.558755271</v>
+        <v>1184504.62323059</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.02101351351351351</v>
+        <v>0.02253623188405797</v>
       </c>
       <c r="B3" t="n">
-        <v>1184503.966015907</v>
+        <v>1192449.496002276</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.04202702702702703</v>
+        <v>0.04507246376811594</v>
       </c>
       <c r="B4" t="n">
-        <v>1184502.373319788</v>
+        <v>1203458.7409311</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>0.06304054054054054</v>
+        <v>0.06760869565217391</v>
       </c>
       <c r="B5" t="n">
-        <v>1184500.780671373</v>
+        <v>1217181.191215642</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.08405405405405406</v>
+        <v>0.09014492753623188</v>
       </c>
       <c r="B6" t="n">
-        <v>1184499.188067362</v>
+        <v>1233258.528965524</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.1050675675675676</v>
+        <v>0.1126811594202898</v>
       </c>
       <c r="B7" t="n">
-        <v>1188624.889518995</v>
+        <v>1251252.210891215</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.1260810810810811</v>
+        <v>0.1352173913043478</v>
       </c>
       <c r="B8" t="n">
-        <v>1196037.932406239</v>
+        <v>1270532.910718079</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.1470945945945946</v>
+        <v>0.1577536231884058</v>
       </c>
       <c r="B9" t="n">
-        <v>1206310.832621991</v>
+        <v>1289745.783588633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.1681081081081081</v>
+        <v>0.1802898550724638</v>
       </c>
       <c r="B10" t="n">
-        <v>1219115.860089636</v>
+        <v>1308251.630263059</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.1891216216216216</v>
+        <v>0.2028260869565217</v>
       </c>
       <c r="B11" t="n">
-        <v>1234118.610894984</v>
+        <v>1325912.826867245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.2101351351351352</v>
+        <v>0.2253623188405797</v>
       </c>
       <c r="B12" t="n">
-        <v>1250909.80994315</v>
+        <v>1342753.172150617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.2311486486486486</v>
+        <v>0.2478985507246377</v>
       </c>
       <c r="B13" t="n">
-        <v>1268902.131918638</v>
+        <v>1358802.462686753</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.2521621621621621</v>
+        <v>0.2704347826086956</v>
       </c>
       <c r="B14" t="n">
-        <v>1286831.754354437</v>
+        <v>1374126.818289812</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.2731756756756757</v>
+        <v>0.2929710144927536</v>
       </c>
       <c r="B15" t="n">
-        <v>1304101.830370369</v>
+        <v>1388781.523580031</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.2941891891891892</v>
+        <v>0.3155072463768116</v>
       </c>
       <c r="B16" t="n">
-        <v>1320583.526531055</v>
+        <v>1402799.603125818</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>0.3152027027027027</v>
+        <v>0.3380434782608696</v>
       </c>
       <c r="B17" t="n">
-        <v>1336298.973586852</v>
+        <v>1416209.254091867</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3362162162162162</v>
+        <v>0.3605797101449275</v>
       </c>
       <c r="B18" t="n">
-        <v>1351275.975424955</v>
+        <v>1429047.981974331</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.3572297297297297</v>
+        <v>0.3831159420289855</v>
       </c>
       <c r="B19" t="n">
-        <v>1365576.237556789</v>
+        <v>1441346.787155742</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.3782432432432433</v>
+        <v>0.4056521739130434</v>
       </c>
       <c r="B20" t="n">
-        <v>1379251.355262874</v>
+        <v>1453132.097818829</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>0.3992567567567568</v>
+        <v>0.4281884057971014</v>
       </c>
       <c r="B21" t="n">
-        <v>1392332.147045669</v>
+        <v>1464427.442380588</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.4202702702702703</v>
+        <v>0.4507246376811594</v>
       </c>
       <c r="B22" t="n">
-        <v>1404844.927592173</v>
+        <v>1475254.334048357</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.4412837837837838</v>
+        <v>0.4732608695652173</v>
       </c>
       <c r="B23" t="n">
-        <v>1416824.69928988</v>
+        <v>1485632.891948085</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.4622972972972973</v>
+        <v>0.4957971014492754</v>
       </c>
       <c r="B24" t="n">
-        <v>1428300.393627381</v>
+        <v>1495582.702949855</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.4833108108108108</v>
+        <v>0.5183333333333333</v>
       </c>
       <c r="B25" t="n">
-        <v>1439296.675552918</v>
+        <v>1505121.778930072</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.5043243243243243</v>
+        <v>0.5408695652173913</v>
       </c>
       <c r="B26" t="n">
-        <v>1449835.50420795</v>
+        <v>1514265.992655779</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5253378378378378</v>
+        <v>0.5634057971014492</v>
       </c>
       <c r="B27" t="n">
-        <v>1459936.958411067</v>
+        <v>1523024.295140531</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.5463513513513514</v>
+        <v>0.5859420289855072</v>
       </c>
       <c r="B28" t="n">
-        <v>1469619.816287918</v>
+        <v>1531414.035454095</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.5673648648648649</v>
+        <v>0.6084782608695651</v>
       </c>
       <c r="B29" t="n">
-        <v>1478902.348621268</v>
+        <v>1539450.697661204</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.5883783783783784</v>
+        <v>0.6310144927536232</v>
       </c>
       <c r="B30" t="n">
-        <v>1487801.384853718</v>
+        <v>1547148.553611261</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.6093918918918919</v>
+        <v>0.6535507246376812</v>
       </c>
       <c r="B31" t="n">
-        <v>1496331.748985978</v>
+        <v>1554520.82654792</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.6304054054054055</v>
+        <v>0.6760869565217391</v>
       </c>
       <c r="B32" t="n">
-        <v>1504501.773703887</v>
+        <v>1561579.949853621</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>0.6514189189189189</v>
+        <v>0.6986231884057971</v>
       </c>
       <c r="B33" t="n">
-        <v>1512327.663302453</v>
+        <v>1568337.691849521</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.6724324324324324</v>
+        <v>0.721159420289855</v>
       </c>
       <c r="B34" t="n">
-        <v>1519823.871808458</v>
+        <v>1574805.241021909</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.693445945945946</v>
+        <v>0.743695652173913</v>
       </c>
       <c r="B35" t="n">
-        <v>1527003.722075782</v>
+        <v>1580993.258143856</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.7144594594594594</v>
+        <v>0.7662318840579709</v>
       </c>
       <c r="B36" t="n">
-        <v>1533879.558465027</v>
+        <v>1586911.912796324</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.735472972972973</v>
+        <v>0.7887681159420289</v>
       </c>
       <c r="B37" t="n">
-        <v>1540462.988292972</v>
+        <v>1592570.916085089</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.7564864864864865</v>
+        <v>0.8113043478260868</v>
       </c>
       <c r="B38" t="n">
-        <v>1546764.998286794</v>
+        <v>1597979.543464819</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.7775</v>
+        <v>0.8338405797101449</v>
       </c>
       <c r="B39" t="n">
-        <v>1552796.034109715</v>
+        <v>1603146.653378205</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.7985135135135135</v>
+        <v>0.8563768115942029</v>
       </c>
       <c r="B40" t="n">
-        <v>1558566.048986903</v>
+        <v>1608080.709320653</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.8195270270270271</v>
+        <v>0.8789130434782608</v>
       </c>
       <c r="B41" t="n">
-        <v>1564084.5377749</v>
+        <v>1612789.790489738</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.8405405405405406</v>
+        <v>0.9014492753623188</v>
       </c>
       <c r="B42" t="n">
-        <v>1569360.567485966</v>
+        <v>1617281.612709643</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.8615540540540541</v>
+        <v>0.9239855072463767</v>
       </c>
       <c r="B43" t="n">
-        <v>1574402.798575398</v>
+        <v>1621563.535276466</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8825675675675676</v>
+        <v>0.9465217391304347</v>
       </c>
       <c r="B44" t="n">
-        <v>1579219.502330292</v>
+        <v>1625642.57922</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.9035810810810811</v>
+        <v>0.9690579710144926</v>
       </c>
       <c r="B45" t="n">
-        <v>1583818.581451547</v>
+        <v>1629525.435672105</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.9245945945945946</v>
+        <v>0.9915942028985507</v>
       </c>
       <c r="B46" t="n">
-        <v>1588207.579988973</v>
+        <v>1633218.477660269</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.9456081081081081</v>
+        <v>1.014130434782609</v>
       </c>
       <c r="B47" t="n">
-        <v>1592393.70285607</v>
+        <v>1636727.775326307</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.9666216216216217</v>
+        <v>1.036666666666667</v>
       </c>
       <c r="B48" t="n">
-        <v>1596383.822219681</v>
+        <v>1640059.108862183</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.9876351351351351</v>
+        <v>1.059202898550724</v>
       </c>
       <c r="B49" t="n">
-        <v>1600184.494538002</v>
+        <v>1643218.011888733</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>1.008648648648649</v>
+        <v>1.081739130434783</v>
       </c>
       <c r="B50" t="n">
-        <v>1603801.96836335</v>
+        <v>1646209.705621694</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>1.029662162162162</v>
+        <v>1.104275362318841</v>
       </c>
       <c r="B51" t="n">
-        <v>1607242.195346294</v>
+        <v>1649039.150812858</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>1.050675675675676</v>
+        <v>1.126811594202898</v>
       </c>
       <c r="B52" t="n">
-        <v>1610510.844438065</v>
+        <v>1651711.41344092</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>1.071689189189189</v>
+        <v>1.149347826086957</v>
       </c>
       <c r="B53" t="n">
-        <v>1613613.31395888</v>
+        <v>1654230.391786249</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>1.092702702702703</v>
+        <v>1.171884057971014</v>
       </c>
       <c r="B54" t="n">
-        <v>1616554.772078578</v>
+        <v>1656599.982837803</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>1.113716216216216</v>
+        <v>1.194420289855072</v>
       </c>
       <c r="B55" t="n">
-        <v>1619340.095377572</v>
+        <v>1658824.021939333</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1.13472972972973</v>
+        <v>1.21695652173913</v>
       </c>
       <c r="B56" t="n">
-        <v>1621973.974361405</v>
+        <v>1660906.06684421</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>1.155743243243243</v>
+        <v>1.239492753623188</v>
       </c>
       <c r="B57" t="n">
-        <v>1624461.0401395</v>
+        <v>1662849.447371786</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>1.176756756756757</v>
+        <v>1.262028985507246</v>
       </c>
       <c r="B58" t="n">
-        <v>1626804.928215442</v>
+        <v>1664657.266548357</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>1.19777027027027</v>
+        <v>1.284565217391304</v>
       </c>
       <c r="B59" t="n">
-        <v>1629009.377551561</v>
+        <v>1666332.40935888</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>1.218783783783784</v>
+        <v>1.307101449275362</v>
       </c>
       <c r="B60" t="n">
-        <v>1631077.923234683</v>
+        <v>1667877.526573803</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>1.239797297297297</v>
+        <v>1.32963768115942</v>
       </c>
       <c r="B61" t="n">
-        <v>1633013.889194754</v>
+        <v>1669295.057961142</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>1.260810810810811</v>
+        <v>1.352173913043478</v>
       </c>
       <c r="B62" t="n">
-        <v>1634820.386610603</v>
+        <v>1670587.224865747</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>1.281824324324324</v>
+        <v>1.374710144927536</v>
       </c>
       <c r="B63" t="n">
-        <v>1636500.314972124</v>
+        <v>1671756.027925727</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>1.302837837837838</v>
+        <v>1.397246376811594</v>
       </c>
       <c r="B64" t="n">
-        <v>1638056.370252702</v>
+        <v>1672803.239842016</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>1.323851351351351</v>
+        <v>1.419782608695652</v>
       </c>
       <c r="B65" t="n">
-        <v>1639491.029815847</v>
+        <v>1673730.388158972</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>1.344864864864865</v>
+        <v>1.44231884057971</v>
       </c>
       <c r="B66" t="n">
-        <v>1640806.574081687</v>
+        <v>1674538.719303708</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>1.365878378378378</v>
+        <v>1.464855072463768</v>
       </c>
       <c r="B67" t="n">
-        <v>1642005.079600535</v>
+        <v>1675229.131992488</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.386891891891892</v>
+        <v>1.487391304347826</v>
       </c>
       <c r="B68" t="n">
-        <v>1643088.416931678</v>
+        <v>1675802.050798222</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>1.407905405405405</v>
+        <v>1.509927536231884</v>
       </c>
       <c r="B69" t="n">
-        <v>1644058.243889884</v>
+        <v>1676257.192122056</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>1.428918918918919</v>
+        <v>1.532463768115942</v>
       </c>
       <c r="B70" t="n">
-        <v>1644915.989488223</v>
+        <v>1676593.134475493</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>1.449932432432433</v>
+        <v>1.555</v>
       </c>
       <c r="B71" t="n">
-        <v>1645662.820375383</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>1.470945945945946</v>
-      </c>
-      <c r="B72" t="n">
-        <v>1646299.578699031</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>1.491959459459459</v>
-      </c>
-      <c r="B73" t="n">
-        <v>1646826.664124586</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>1.512972972972973</v>
-      </c>
-      <c r="B74" t="n">
-        <v>1647243.815441396</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>1.533986486486487</v>
-      </c>
-      <c r="B75" t="n">
-        <v>1647549.709566471</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>1.555</v>
-      </c>
-      <c r="B76" t="n">
-        <v>1647741.22092092</v>
+        <v>1676797.880121854</v>
       </c>
     </row>
   </sheetData>
